--- a/talavera_hub_riders.xlsx
+++ b/talavera_hub_riders.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\website\spx_talavera\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0293410A-E9D9-4284-B375-5F8AAE73A6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -460,222 +466,6 @@
     <t>Yull Eric Talon Luquias</t>
   </si>
   <si>
-    <t>9758230662</t>
-  </si>
-  <si>
-    <t>9950250710</t>
-  </si>
-  <si>
-    <t>9647669198</t>
-  </si>
-  <si>
-    <t>9159007960</t>
-  </si>
-  <si>
-    <t>9161081496</t>
-  </si>
-  <si>
-    <t>9174277508</t>
-  </si>
-  <si>
-    <t>9814569731</t>
-  </si>
-  <si>
-    <t>9817255070</t>
-  </si>
-  <si>
-    <t>9925869327</t>
-  </si>
-  <si>
-    <t>9913722951</t>
-  </si>
-  <si>
-    <t>9302650130</t>
-  </si>
-  <si>
-    <t>9569186453</t>
-  </si>
-  <si>
-    <t>9616165116</t>
-  </si>
-  <si>
-    <t>9260145154</t>
-  </si>
-  <si>
-    <t>9265329439</t>
-  </si>
-  <si>
-    <t>9914118427</t>
-  </si>
-  <si>
-    <t>9751484202</t>
-  </si>
-  <si>
-    <t>9676847483</t>
-  </si>
-  <si>
-    <t>9261951945</t>
-  </si>
-  <si>
-    <t>9662952705</t>
-  </si>
-  <si>
-    <t>9366388294</t>
-  </si>
-  <si>
-    <t>9975534736</t>
-  </si>
-  <si>
-    <t>9355340726</t>
-  </si>
-  <si>
-    <t>9773912206</t>
-  </si>
-  <si>
-    <t>9153111043</t>
-  </si>
-  <si>
-    <t>9978451908</t>
-  </si>
-  <si>
-    <t>9914383908</t>
-  </si>
-  <si>
-    <t>9557267270</t>
-  </si>
-  <si>
-    <t>9128460869</t>
-  </si>
-  <si>
-    <t>9692555545</t>
-  </si>
-  <si>
-    <t>9556571226</t>
-  </si>
-  <si>
-    <t>9264357475</t>
-  </si>
-  <si>
-    <t>9551156658</t>
-  </si>
-  <si>
-    <t>9453410692</t>
-  </si>
-  <si>
-    <t>9526137275</t>
-  </si>
-  <si>
-    <t>9932817329</t>
-  </si>
-  <si>
-    <t>9459678562</t>
-  </si>
-  <si>
-    <t>9567502953</t>
-  </si>
-  <si>
-    <t>9090551374</t>
-  </si>
-  <si>
-    <t>9559913624</t>
-  </si>
-  <si>
-    <t>9505084507</t>
-  </si>
-  <si>
-    <t>9152893529</t>
-  </si>
-  <si>
-    <t>9270064783</t>
-  </si>
-  <si>
-    <t>9456903476</t>
-  </si>
-  <si>
-    <t>9675282119</t>
-  </si>
-  <si>
-    <t>9154803454</t>
-  </si>
-  <si>
-    <t>9157743394</t>
-  </si>
-  <si>
-    <t>9171328302</t>
-  </si>
-  <si>
-    <t>9551988085</t>
-  </si>
-  <si>
-    <t>9060290045</t>
-  </si>
-  <si>
-    <t>9268560656</t>
-  </si>
-  <si>
-    <t>9265709351</t>
-  </si>
-  <si>
-    <t>9478517061</t>
-  </si>
-  <si>
-    <t>9355590991</t>
-  </si>
-  <si>
-    <t>9556549195</t>
-  </si>
-  <si>
-    <t>9355564716</t>
-  </si>
-  <si>
-    <t>9354938951</t>
-  </si>
-  <si>
-    <t>9564423525</t>
-  </si>
-  <si>
-    <t>9350287878</t>
-  </si>
-  <si>
-    <t>9656148264</t>
-  </si>
-  <si>
-    <t>9513407050</t>
-  </si>
-  <si>
-    <t>9676031590</t>
-  </si>
-  <si>
-    <t>9532982051</t>
-  </si>
-  <si>
-    <t>9975788851</t>
-  </si>
-  <si>
-    <t>9269787949</t>
-  </si>
-  <si>
-    <t>9263626553</t>
-  </si>
-  <si>
-    <t>9652995832</t>
-  </si>
-  <si>
-    <t>9068919861</t>
-  </si>
-  <si>
-    <t>9541038395</t>
-  </si>
-  <si>
-    <t>9656038228</t>
-  </si>
-  <si>
-    <t>9261118196</t>
-  </si>
-  <si>
-    <t>9532516498</t>
-  </si>
-  <si>
     <t>3WC</t>
   </si>
   <si>
@@ -689,13 +479,229 @@
   </si>
   <si>
     <t>4WAUV</t>
+  </si>
+  <si>
+    <t>09758230662</t>
+  </si>
+  <si>
+    <t>09950250710</t>
+  </si>
+  <si>
+    <t>09647669198</t>
+  </si>
+  <si>
+    <t>09159007960</t>
+  </si>
+  <si>
+    <t>09161081496</t>
+  </si>
+  <si>
+    <t>09174277508</t>
+  </si>
+  <si>
+    <t>09814569731</t>
+  </si>
+  <si>
+    <t>09817255070</t>
+  </si>
+  <si>
+    <t>09925869327</t>
+  </si>
+  <si>
+    <t>09913722951</t>
+  </si>
+  <si>
+    <t>09302650130</t>
+  </si>
+  <si>
+    <t>09569186453</t>
+  </si>
+  <si>
+    <t>09616165116</t>
+  </si>
+  <si>
+    <t>09260145154</t>
+  </si>
+  <si>
+    <t>09265329439</t>
+  </si>
+  <si>
+    <t>09914118427</t>
+  </si>
+  <si>
+    <t>09751484202</t>
+  </si>
+  <si>
+    <t>09676847483</t>
+  </si>
+  <si>
+    <t>09261951945</t>
+  </si>
+  <si>
+    <t>09662952705</t>
+  </si>
+  <si>
+    <t>09366388294</t>
+  </si>
+  <si>
+    <t>09975534736</t>
+  </si>
+  <si>
+    <t>09355340726</t>
+  </si>
+  <si>
+    <t>09773912206</t>
+  </si>
+  <si>
+    <t>09153111043</t>
+  </si>
+  <si>
+    <t>09978451908</t>
+  </si>
+  <si>
+    <t>09914383908</t>
+  </si>
+  <si>
+    <t>09557267270</t>
+  </si>
+  <si>
+    <t>09128460869</t>
+  </si>
+  <si>
+    <t>09692555545</t>
+  </si>
+  <si>
+    <t>09556571226</t>
+  </si>
+  <si>
+    <t>09264357475</t>
+  </si>
+  <si>
+    <t>09551156658</t>
+  </si>
+  <si>
+    <t>09453410692</t>
+  </si>
+  <si>
+    <t>09526137275</t>
+  </si>
+  <si>
+    <t>09932817329</t>
+  </si>
+  <si>
+    <t>09459678562</t>
+  </si>
+  <si>
+    <t>09567502953</t>
+  </si>
+  <si>
+    <t>09090551374</t>
+  </si>
+  <si>
+    <t>09559913624</t>
+  </si>
+  <si>
+    <t>09505084507</t>
+  </si>
+  <si>
+    <t>09152893529</t>
+  </si>
+  <si>
+    <t>09270064783</t>
+  </si>
+  <si>
+    <t>09456903476</t>
+  </si>
+  <si>
+    <t>09675282119</t>
+  </si>
+  <si>
+    <t>09154803454</t>
+  </si>
+  <si>
+    <t>09157743394</t>
+  </si>
+  <si>
+    <t>09171328302</t>
+  </si>
+  <si>
+    <t>09551988085</t>
+  </si>
+  <si>
+    <t>09060290045</t>
+  </si>
+  <si>
+    <t>09268560656</t>
+  </si>
+  <si>
+    <t>09265709351</t>
+  </si>
+  <si>
+    <t>09478517061</t>
+  </si>
+  <si>
+    <t>09355590991</t>
+  </si>
+  <si>
+    <t>09556549195</t>
+  </si>
+  <si>
+    <t>09355564716</t>
+  </si>
+  <si>
+    <t>09354938951</t>
+  </si>
+  <si>
+    <t>09564423525</t>
+  </si>
+  <si>
+    <t>09350287878</t>
+  </si>
+  <si>
+    <t>09656148264</t>
+  </si>
+  <si>
+    <t>09513407050</t>
+  </si>
+  <si>
+    <t>09676031590</t>
+  </si>
+  <si>
+    <t>09532982051</t>
+  </si>
+  <si>
+    <t>09975788851</t>
+  </si>
+  <si>
+    <t>09269787949</t>
+  </si>
+  <si>
+    <t>09263626553</t>
+  </si>
+  <si>
+    <t>09652995832</t>
+  </si>
+  <si>
+    <t>09068919861</t>
+  </si>
+  <si>
+    <t>09541038395</t>
+  </si>
+  <si>
+    <t>09656038228</t>
+  </si>
+  <si>
+    <t>09261118196</t>
+  </si>
+  <si>
+    <t>09532516498</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -747,24 +753,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -802,7 +817,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -836,6 +851,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -870,9 +886,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1045,11 +1062,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,1012 +1085,1012 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>148</v>
+      <c r="C2" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" t="s">
-        <v>149</v>
+      <c r="C3" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
-      <c r="C4" t="s">
-        <v>150</v>
+      <c r="C4" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" t="s">
-        <v>151</v>
+      <c r="C5" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" t="s">
-        <v>152</v>
+      <c r="C6" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
-      <c r="C7" t="s">
-        <v>153</v>
+      <c r="C7" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
-      <c r="C8" t="s">
-        <v>154</v>
+      <c r="C8" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>83</v>
       </c>
-      <c r="C9" t="s">
-        <v>155</v>
+      <c r="C9" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>84</v>
       </c>
-      <c r="C10" t="s">
-        <v>156</v>
+      <c r="C10" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
-        <v>157</v>
+      <c r="C11" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>86</v>
       </c>
-      <c r="C12" t="s">
-        <v>158</v>
+      <c r="C12" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
-        <v>159</v>
+      <c r="C13" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" t="s">
-        <v>160</v>
+      <c r="C14" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>89</v>
       </c>
-      <c r="C15" t="s">
-        <v>161</v>
+      <c r="C15" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>90</v>
       </c>
-      <c r="C16" t="s">
-        <v>162</v>
+      <c r="C16" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
       </c>
-      <c r="C17" t="s">
-        <v>163</v>
+      <c r="C17" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>92</v>
       </c>
-      <c r="C18" t="s">
-        <v>164</v>
+      <c r="C18" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
       </c>
-      <c r="C19" t="s">
-        <v>165</v>
+      <c r="C19" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>94</v>
       </c>
-      <c r="C20" t="s">
-        <v>166</v>
+      <c r="C20" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>95</v>
       </c>
-      <c r="C21" t="s">
-        <v>167</v>
+      <c r="C21" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>96</v>
       </c>
-      <c r="C22" t="s">
-        <v>168</v>
+      <c r="C22" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
-      <c r="C23" t="s">
-        <v>169</v>
+      <c r="C23" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>98</v>
       </c>
-      <c r="C24" t="s">
-        <v>170</v>
+      <c r="C24" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s">
-        <v>171</v>
+      <c r="C25" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>100</v>
       </c>
-      <c r="C26" t="s">
-        <v>172</v>
+      <c r="C26" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="D26" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>101</v>
       </c>
-      <c r="C27" t="s">
-        <v>173</v>
+      <c r="C27" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>102</v>
       </c>
-      <c r="C28" t="s">
-        <v>174</v>
+      <c r="C28" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="D28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>103</v>
       </c>
-      <c r="C29" t="s">
-        <v>175</v>
+      <c r="C29" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>104</v>
       </c>
-      <c r="C30" t="s">
-        <v>176</v>
+      <c r="C30" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C31" t="s">
-        <v>177</v>
+      <c r="C31" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="D31" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>106</v>
       </c>
-      <c r="C32" t="s">
-        <v>178</v>
+      <c r="C32" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>107</v>
       </c>
-      <c r="C33" t="s">
-        <v>179</v>
+      <c r="C33" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>108</v>
       </c>
-      <c r="C34" t="s">
-        <v>180</v>
+      <c r="C34" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="D34" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
-      <c r="C35" t="s">
-        <v>181</v>
+      <c r="C35" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="D35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
         <v>110</v>
       </c>
-      <c r="C36" t="s">
-        <v>182</v>
+      <c r="C36" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="D36" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37" t="s">
         <v>111</v>
       </c>
-      <c r="C37" t="s">
-        <v>183</v>
+      <c r="C37" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>112</v>
       </c>
-      <c r="C38" t="s">
-        <v>184</v>
+      <c r="C38" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
       <c r="B39" t="s">
         <v>113</v>
       </c>
-      <c r="C39" t="s">
-        <v>185</v>
+      <c r="C39" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>114</v>
       </c>
-      <c r="C40" t="s">
-        <v>186</v>
+      <c r="C40" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
       <c r="B41" t="s">
         <v>115</v>
       </c>
-      <c r="C41" t="s">
-        <v>187</v>
+      <c r="C41" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
       <c r="B42" t="s">
         <v>116</v>
       </c>
-      <c r="C42" t="s">
-        <v>188</v>
+      <c r="C42" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
       <c r="B43" t="s">
         <v>117</v>
       </c>
-      <c r="C43" t="s">
-        <v>189</v>
+      <c r="C43" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="D43" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
       <c r="B44" t="s">
         <v>118</v>
       </c>
-      <c r="C44" t="s">
-        <v>190</v>
+      <c r="C44" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>119</v>
       </c>
-      <c r="C45" t="s">
-        <v>191</v>
+      <c r="C45" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="D45" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>120</v>
       </c>
-      <c r="C46" t="s">
-        <v>192</v>
+      <c r="C46" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
         <v>121</v>
       </c>
-      <c r="C47" t="s">
-        <v>193</v>
+      <c r="C47" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
       <c r="B48" t="s">
         <v>122</v>
       </c>
-      <c r="C48" t="s">
-        <v>194</v>
+      <c r="C48" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
       <c r="B49" t="s">
         <v>123</v>
       </c>
-      <c r="C49" t="s">
-        <v>195</v>
+      <c r="C49" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50" t="s">
         <v>124</v>
       </c>
-      <c r="C50" t="s">
-        <v>196</v>
+      <c r="C50" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="D50" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
       <c r="B51" t="s">
         <v>125</v>
       </c>
-      <c r="C51" t="s">
-        <v>197</v>
+      <c r="C51" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="D51" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
       <c r="B52" t="s">
         <v>126</v>
       </c>
-      <c r="C52" t="s">
-        <v>198</v>
+      <c r="C52" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="D52" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
       <c r="B53" t="s">
         <v>127</v>
       </c>
-      <c r="C53" t="s">
-        <v>199</v>
+      <c r="C53" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
       <c r="B54" t="s">
         <v>128</v>
       </c>
-      <c r="C54" t="s">
-        <v>200</v>
+      <c r="C54" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="D54" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
       <c r="B55" t="s">
         <v>129</v>
       </c>
-      <c r="C55" t="s">
-        <v>201</v>
+      <c r="C55" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
       <c r="B56" t="s">
         <v>130</v>
       </c>
-      <c r="C56" t="s">
-        <v>202</v>
+      <c r="C56" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
       <c r="B57" t="s">
         <v>131</v>
       </c>
-      <c r="C57" t="s">
-        <v>203</v>
+      <c r="C57" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
       <c r="B58" t="s">
         <v>132</v>
       </c>
-      <c r="C58" t="s">
-        <v>204</v>
+      <c r="C58" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
       <c r="B59" t="s">
         <v>133</v>
       </c>
-      <c r="C59" t="s">
-        <v>205</v>
+      <c r="C59" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
       <c r="B60" t="s">
         <v>134</v>
       </c>
-      <c r="C60" t="s">
-        <v>206</v>
+      <c r="C60" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
       <c r="B61" t="s">
         <v>135</v>
       </c>
-      <c r="C61" t="s">
-        <v>207</v>
+      <c r="C61" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="D61" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
       <c r="B62" t="s">
         <v>136</v>
       </c>
-      <c r="C62" t="s">
-        <v>208</v>
+      <c r="C62" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="D62" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>137</v>
       </c>
-      <c r="C63" t="s">
-        <v>209</v>
+      <c r="C63" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="D63" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
       </c>
-      <c r="C64" t="s">
-        <v>210</v>
+      <c r="C64" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="D64" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
       <c r="B65" t="s">
         <v>139</v>
       </c>
-      <c r="C65" t="s">
-        <v>211</v>
+      <c r="C65" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="D65" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
       <c r="B66" t="s">
         <v>140</v>
       </c>
-      <c r="C66" t="s">
-        <v>212</v>
+      <c r="C66" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="D66" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
       <c r="B67" t="s">
         <v>141</v>
       </c>
-      <c r="C67" t="s">
-        <v>213</v>
+      <c r="C67" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="D67" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
       <c r="B68" t="s">
         <v>142</v>
       </c>
-      <c r="C68" t="s">
-        <v>214</v>
+      <c r="C68" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="D68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
       <c r="B69" t="s">
         <v>143</v>
       </c>
-      <c r="C69" t="s">
-        <v>215</v>
+      <c r="C69" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="D69" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
       <c r="B70" t="s">
         <v>144</v>
       </c>
-      <c r="C70" t="s">
-        <v>216</v>
+      <c r="C70" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
         <v>145</v>
       </c>
-      <c r="C71" t="s">
-        <v>217</v>
+      <c r="C71" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="D71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
       <c r="B72" t="s">
         <v>146</v>
       </c>
-      <c r="C72" t="s">
-        <v>218</v>
+      <c r="C72" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
       <c r="B73" t="s">
         <v>147</v>
       </c>
-      <c r="C73" t="s">
-        <v>219</v>
+      <c r="C73" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/talavera_hub_riders.xlsx
+++ b/talavera_hub_riders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\website\spx_talavera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0293410A-E9D9-4284-B375-5F8AAE73A6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AA35A4-CFBC-4126-AF9A-9CF51DD1435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="236">
   <si>
     <t>Driver ID</t>
   </si>
@@ -695,6 +695,39 @@
   </si>
   <si>
     <t>09532516498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erwin </t>
+  </si>
+  <si>
+    <t>09551980836</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>09972443997</t>
+  </si>
+  <si>
+    <t>RYAN PAGAL CAMBE</t>
+  </si>
+  <si>
+    <t>09751850837</t>
+  </si>
+  <si>
+    <t>Ronald pagkanlungan</t>
+  </si>
+  <si>
+    <t>09556583422</t>
+  </si>
+  <si>
+    <t>elmer flexi</t>
+  </si>
+  <si>
+    <t>09536477523</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -2093,6 +2126,76 @@
         <v>149</v>
       </c>
     </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" t="s">
+        <v>225</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D74" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" t="s">
+        <v>227</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D75" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>228</v>
+      </c>
+      <c r="B76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D76" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>228</v>
+      </c>
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>228</v>
+      </c>
+      <c r="B78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D78" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/talavera_hub_riders.xlsx
+++ b/talavera_hub_riders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\website\spx_talavera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AA35A4-CFBC-4126-AF9A-9CF51DD1435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31757E9-992D-46E4-A301-54460A0D9A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="242">
   <si>
     <t>Driver ID</t>
   </si>
@@ -508,9 +508,6 @@
     <t>09925869327</t>
   </si>
   <si>
-    <t>09913722951</t>
-  </si>
-  <si>
     <t>09302650130</t>
   </si>
   <si>
@@ -628,9 +625,6 @@
     <t>09551988085</t>
   </si>
   <si>
-    <t>09060290045</t>
-  </si>
-  <si>
     <t>09268560656</t>
   </si>
   <si>
@@ -728,13 +722,40 @@
   </si>
   <si>
     <t>09536477523</t>
+  </si>
+  <si>
+    <t>Antonio Jr Soriano Agliam</t>
+  </si>
+  <si>
+    <t>flexi tasic</t>
+  </si>
+  <si>
+    <t>09654432031</t>
+  </si>
+  <si>
+    <t>09067830952</t>
+  </si>
+  <si>
+    <t>Christian Guillermo</t>
+  </si>
+  <si>
+    <t>TL</t>
+  </si>
+  <si>
+    <t>Frehelson Bibe</t>
+  </si>
+  <si>
+    <t>Backroom</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="00000000000"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,6 +767,32 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF080809"/>
+      <name val="Segoe UI Historic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF303844"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF080809"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -786,12 +833,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1096,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -1252,7 +1304,7 @@
         <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D11" t="s">
         <v>149</v>
@@ -1266,7 +1318,7 @@
         <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -1280,7 +1332,7 @@
         <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
         <v>148</v>
@@ -1294,7 +1346,7 @@
         <v>88</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
         <v>148</v>
@@ -1308,7 +1360,7 @@
         <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
         <v>148</v>
@@ -1322,7 +1374,7 @@
         <v>90</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
         <v>148</v>
@@ -1336,7 +1388,7 @@
         <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D17" t="s">
         <v>149</v>
@@ -1350,7 +1402,7 @@
         <v>92</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>148</v>
@@ -1364,7 +1416,7 @@
         <v>93</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
         <v>148</v>
@@ -1378,7 +1430,7 @@
         <v>94</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
         <v>148</v>
@@ -1392,7 +1444,7 @@
         <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
         <v>148</v>
@@ -1406,7 +1458,7 @@
         <v>96</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D22" t="s">
         <v>150</v>
@@ -1420,7 +1472,7 @@
         <v>97</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -1434,7 +1486,7 @@
         <v>98</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -1448,7 +1500,7 @@
         <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D25" t="s">
         <v>148</v>
@@ -1462,7 +1514,7 @@
         <v>100</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D26" t="s">
         <v>148</v>
@@ -1476,7 +1528,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -1490,7 +1542,7 @@
         <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D28" t="s">
         <v>151</v>
@@ -1504,7 +1556,7 @@
         <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D29" t="s">
         <v>148</v>
@@ -1518,7 +1570,7 @@
         <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D30" t="s">
         <v>148</v>
@@ -1532,7 +1584,7 @@
         <v>105</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
         <v>148</v>
@@ -1546,7 +1598,7 @@
         <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -1560,7 +1612,7 @@
         <v>107</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D33" t="s">
         <v>148</v>
@@ -1574,7 +1626,7 @@
         <v>108</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -1588,7 +1640,7 @@
         <v>109</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -1602,7 +1654,7 @@
         <v>110</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
         <v>148</v>
@@ -1616,7 +1668,7 @@
         <v>111</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
         <v>149</v>
@@ -1630,7 +1682,7 @@
         <v>112</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
         <v>148</v>
@@ -1644,7 +1696,7 @@
         <v>113</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
         <v>148</v>
@@ -1658,7 +1710,7 @@
         <v>114</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
         <v>148</v>
@@ -1672,7 +1724,7 @@
         <v>115</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D41" t="s">
         <v>148</v>
@@ -1686,7 +1738,7 @@
         <v>116</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D42" t="s">
         <v>149</v>
@@ -1700,7 +1752,7 @@
         <v>117</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D43" t="s">
         <v>149</v>
@@ -1714,7 +1766,7 @@
         <v>118</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D44" t="s">
         <v>151</v>
@@ -1728,7 +1780,7 @@
         <v>119</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D45" t="s">
         <v>148</v>
@@ -1742,7 +1794,7 @@
         <v>120</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
         <v>149</v>
@@ -1756,7 +1808,7 @@
         <v>121</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D47" t="s">
         <v>148</v>
@@ -1770,7 +1822,7 @@
         <v>122</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
         <v>150</v>
@@ -1784,7 +1836,7 @@
         <v>123</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D49" t="s">
         <v>152</v>
@@ -1798,7 +1850,7 @@
         <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D50" t="s">
         <v>149</v>
@@ -1812,7 +1864,7 @@
         <v>125</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
         <v>148</v>
@@ -1826,7 +1878,7 @@
         <v>126</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s">
         <v>149</v>
@@ -1840,7 +1892,7 @@
         <v>127</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D53" t="s">
         <v>149</v>
@@ -1854,7 +1906,7 @@
         <v>128</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D54" t="s">
         <v>148</v>
@@ -1868,7 +1920,7 @@
         <v>129</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D55" t="s">
         <v>149</v>
@@ -1882,7 +1934,7 @@
         <v>130</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D56" t="s">
         <v>148</v>
@@ -1896,7 +1948,7 @@
         <v>131</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
         <v>148</v>
@@ -1910,7 +1962,7 @@
         <v>132</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D58" t="s">
         <v>149</v>
@@ -1924,7 +1976,7 @@
         <v>133</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D59" t="s">
         <v>148</v>
@@ -1938,7 +1990,7 @@
         <v>134</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D60" t="s">
         <v>149</v>
@@ -1952,7 +2004,7 @@
         <v>135</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D61" t="s">
         <v>148</v>
@@ -1966,7 +2018,7 @@
         <v>136</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D62" t="s">
         <v>149</v>
@@ -1980,7 +2032,7 @@
         <v>137</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D63" t="s">
         <v>148</v>
@@ -1994,7 +2046,7 @@
         <v>138</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -2008,7 +2060,7 @@
         <v>139</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
         <v>148</v>
@@ -2022,7 +2074,7 @@
         <v>140</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
         <v>148</v>
@@ -2036,7 +2088,7 @@
         <v>141</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D67" t="s">
         <v>148</v>
@@ -2050,7 +2102,7 @@
         <v>142</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D68" t="s">
         <v>151</v>
@@ -2064,7 +2116,7 @@
         <v>143</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D69" t="s">
         <v>148</v>
@@ -2078,7 +2130,7 @@
         <v>144</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D70" t="s">
         <v>149</v>
@@ -2092,7 +2144,7 @@
         <v>145</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D71" t="s">
         <v>148</v>
@@ -2106,7 +2158,7 @@
         <v>146</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D72" t="s">
         <v>148</v>
@@ -2120,7 +2172,7 @@
         <v>147</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D73" t="s">
         <v>149</v>
@@ -2128,41 +2180,41 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B74" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D74" t="s">
         <v>226</v>
-      </c>
-      <c r="D74" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B75" t="s">
+        <v>225</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="D75" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" t="s">
         <v>228</v>
       </c>
-      <c r="B76" t="s">
-        <v>230</v>
-      </c>
       <c r="C76" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D76" t="s">
         <v>149</v>
@@ -2170,30 +2222,77 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B77" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B78" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>320680</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="6">
+        <v>9669928344</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B80" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D78" t="s">
-        <v>228</v>
+      <c r="C80" s="6">
+        <v>9264194080</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" s="6">
+        <v>9565972793</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>240</v>
+      </c>
+      <c r="C82" s="6">
+        <v>9454319340</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
